--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/jun-2026.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/jun-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>709.34</v>
+        <v>717.09</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>10840.59</v>
+        <v>10958.97</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>37372.82</v>
+        <v>37700.6</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>37755.97</v>
+        <v>38298.12</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>1386.01</v>
+        <v>1405.91</v>
       </c>
     </row>
     <row r="7">
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>443479.78</v>
+        <v>449847.9</v>
       </c>
     </row>
     <row r="8">
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>31284.27</v>
+        <v>31536.21</v>
       </c>
     </row>
     <row r="9">
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>4752.04</v>
+        <v>4788.56</v>
       </c>
     </row>
     <row r="10">
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>799431.89</v>
+        <v>805575.1800000001</v>
       </c>
     </row>
     <row r="11">
@@ -1130,7 +1130,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1095642.44</v>
+        <v>1086862.81</v>
       </c>
     </row>
     <row r="12">
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>8019.07</v>
+        <v>8058.6</v>
       </c>
     </row>
     <row r="13">
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>7227.06</v>
+        <v>7338</v>
       </c>
     </row>
     <row r="14">
@@ -1317,7 +1317,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>281162.42</v>
+        <v>286656.49</v>
       </c>
     </row>
     <row r="15">
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>51084.44</v>
+        <v>51470.7</v>
       </c>
     </row>
     <row r="16">
@@ -1439,7 +1439,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>10395.09</v>
+        <v>10377.13</v>
       </c>
     </row>
     <row r="17">
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>314822.71</v>
+        <v>310935.41</v>
       </c>
     </row>
     <row r="18">
@@ -1561,7 +1561,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>4036.47</v>
+        <v>3981.12</v>
       </c>
     </row>
     <row r="19">
@@ -1622,7 +1622,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>1218.29</v>
+        <v>1201.58</v>
       </c>
     </row>
     <row r="20">
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>37471.82</v>
+        <v>36957.96</v>
       </c>
     </row>
     <row r="21">
@@ -1744,7 +1744,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>61479.53</v>
+        <v>60299.47</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/jun-2026.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/jun-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC jun-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC jun-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">

--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/jun-2026.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/jun-2026.xlsx
@@ -914,7 +914,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gobierno Regional de Arica y Parinacota</t>
+          <t>GOBIERNO REGIONAL DE ARICA-PARINACOTA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fondo de Bienestar de la Corporación de Fomento </t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Servicio de Bienestar del Personal del Gobierno Re</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bienestar SSFFAA</t>
+          <t>SUBSECRETARIA PARA LAS FUERZAS ARMADAS</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>BIENESTAR DEL CONSEJO DE DEFENSA DEL ESTADO</t>
+          <t>Consejo de Defensa del Estado</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">

--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/jun-2026.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/jun-2026.xlsx
@@ -562,7 +562,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -932,7 +952,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -993,7 +1017,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1184,7 +1212,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1245,7 +1277,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1371,7 +1407,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1432,7 +1472,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1493,7 +1537,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1554,7 +1602,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1615,7 +1667,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1676,7 +1732,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1737,7 +1797,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/jun-2026.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/jun-2026.xlsx
@@ -1249,7 +1249,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
